--- a/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Worker Configuration</t>
+          <t>Onboarding Ticket Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,85 +671,85 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Worker Provision Settings</t>
+          <t>Sensitive Fields Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPN3327V11YXB95CHXEXJXBT</t>
+          <t>h_01KPQER5CHXADX35D41FBKCFQS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPN3327V11YXB95CHXEXJXBT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQER5CHXADX35D41FBKCFQS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Create Worker Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>h_01KPQER5CHE4JRPA0ND0WTP0TZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQER5CHE4JRPA0ND0WTP0TZ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Club Number Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KPN9K91KTY4DNPFR4B8SYHJ9</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPN9K91KTY4DNPFR4B8SYHJ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R0FP05Q2AS6CBBX3DK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Transaction Template Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,151 +847,151 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Create Transaction Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KPQC1R5CS7NX5V5N8YXP4JET</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQC1R5CS7NX5V5N8YXP4JET</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Update Transaction Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KPQD0SGWKNJXT5CAAPT8GBGF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWKNJXT5CAAPT8GBGF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Delete Transaction Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KPQD0SGWJ17WEYEXGSM62GW8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWJ17WEYEXGSM62GW8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Deactivate Transaction Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KPQD0SGWABMNSJ78V9TAE6ZK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWABMNSJ78V9TAE6ZK</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R0KRGFBZT7S9T8WTDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K04HD998SCMWKJ7BWM43V581</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,54 +1023,76 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K06FVR3HY5TQCJK1AC2W07CZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KPQER5CHXADX35D41FBKCFQS</t>
+          <t>h_01KPQRAZWFJTJZVBHKDFYB35J8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQER5CHXADX35D41FBKCFQS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQRAZWFJTJZVBHKDFYB35J8</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPQER5CHE4JRPA0ND0WTP0TZ</t>
+          <t>h_01KPQRAZWFSM7S1FFW22HC5QZ2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQER5CHE4JRPA0ND0WTP0TZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQRAZWFSM7S1FFW22HC5QZ2</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Scenarios</t>
+          <t>Integration Features</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
+++ b/site/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/headings.xlsx
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Successful Execution</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Transaction Template Settings</t>
+          <t>Failed Execution</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Create Transaction Notification Settings</t>
+          <t>Transaction Template Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KPQC1R5CS7NX5V5N8YXP4JET</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQC1R5CS7NX5V5N8YXP4JET</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Update Transaction Notification Settings</t>
+          <t>Create Transaction Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KPQD0SGWKNJXT5CAAPT8GBGF</t>
+          <t>h_01KPQC1R5CS7NX5V5N8YXP4JET</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWKNJXT5CAAPT8GBGF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQC1R5CS7NX5V5N8YXP4JET</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Delete Transaction Notification Settings</t>
+          <t>Update Transaction Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KPQD0SGWJ17WEYEXGSM62GW8</t>
+          <t>h_01KPQD0SGWKNJXT5CAAPT8GBGF</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWJ17WEYEXGSM62GW8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWKNJXT5CAAPT8GBGF</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deactivate Transaction Notification Settings</t>
+          <t>Delete Transaction Execution</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,34 +935,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KPQD0SGWABMNSJ78V9TAE6ZK</t>
+          <t>h_01KPQD0SGWJ17WEYEXGSM62GW8</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWABMNSJ78V9TAE6ZK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWJ17WEYEXGSM62GW8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Deactivate Transaction Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KPQD0SGWABMNSJ78V9TAE6ZK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Recruiting-Management-ManageEngine-ServiceDesk-Integration-Guide/#h_01KPQD0SGWABMNSJ78V9TAE6ZK</t>
         </is>
       </c>
     </row>
